--- a/apps/be/reports/ImpactCocoa_Filter_Specification.xlsx
+++ b/apps/be/reports/ImpactCocoa_Filter_Specification.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://thinkdataservicesltd.sharepoint.com/sites/ThinkDataServicesIntranet/Shared Documents/SERVICE DELIVERY/PROJECTS/Custom development/AgroEco/ImpactCocoa Database Dev - shared folder/Reporting templates/For review/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://thinkdataservicesltd.sharepoint.com/sites/ThinkDataServicesIntranet/Shared Documents/SERVICE DELIVERY/PROJECTS/Custom development/Think!Data/Think!Cocoa Database Dev - shared folder/Reporting templates/For review/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="11" documentId="8_{D5FFAAE4-2BE7-4D03-ABA7-95B5D85878C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84435512-CBDA-4A8A-9514-85CE2B41CA62}"/>
@@ -42,7 +42,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="96">
   <si>
-    <t>ImpactCocoa Platform — Generic Report Filter Specification</t>
+    <t>Think!Cocoa Platform — Generic Report Filter Specification</t>
   </si>
   <si>
     <t>One shared filter bar renders across all filtered report views. Irrelevant filters are hidden (not greyed out) per report.</t>
@@ -165,7 +165,7 @@
     <t>❌  Hide</t>
   </si>
   <si>
-    <t>ImpactCocoa Platform — Developer Implementation Guidance: Generic Filter Component</t>
+    <t>Think!Cocoa Platform — Developer Implementation Guidance: Generic Filter Component</t>
   </si>
   <si>
     <t>Build one reusable filter component. Each report activates only the relevant filters. Do not build separate filter logic per report.</t>
@@ -258,7 +258,7 @@
     <t>PDF</t>
   </si>
   <si>
-    <t>Server-side render. Include report title, active filter summary (e.g. 'Cooperative: Assin Fosu | Season: 2025/2026 | Date: 01 Jan – 30 Apr 2026'), page numbers, and Think! Data / AgroEco logo in header. Use A4 landscape for wide tables.</t>
+    <t>Server-side render. Include report title, active filter summary (e.g. 'Cooperative: Assin Fosu | Season: 2025/2026 | Date: 01 Jan – 30 Apr 2026'), page numbers, and Think! Data / Think!Data logo in header. Use A4 landscape for wide tables.</t>
   </si>
   <si>
     <t>Excel</t>
